--- a/shein.xlsx
+++ b/shein.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Tool-Buy-Shein\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F6566D-413D-494B-AC28-DB2015C96A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17676B11-DD2D-440C-A828-8C21197EDD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91B14417-4F65-4B5F-82C0-EBB1C5344353}"/>
+    <workbookView xWindow="3510" yWindow="3495" windowWidth="21600" windowHeight="11295" xr2:uid="{91B14417-4F65-4B5F-82C0-EBB1C5344353}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,145 +35,13 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="9">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="6"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="9">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-    <bk>
-      <rc t="1" v="1"/>
-    </bk>
-    <bk>
-      <rc t="1" v="2"/>
-    </bk>
-    <bk>
-      <rc t="1" v="3"/>
-    </bk>
-    <bk>
-      <rc t="1" v="4"/>
-    </bk>
-    <bk>
-      <rc t="1" v="5"/>
-    </bk>
-    <bk>
-      <rc t="1" v="6"/>
-    </bk>
-    <bk>
-      <rc t="1" v="7"/>
-    </bk>
-    <bk>
-      <rc t="1" v="8"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="76">
-  <si>
-    <t>name acc</t>
-  </si>
-  <si>
-    <t>ID ORDER</t>
-  </si>
-  <si>
-    <t>ID Order shein</t>
-  </si>
-  <si>
-    <t>Mail</t>
-  </si>
-  <si>
-    <t>TRACKING</t>
-  </si>
-  <si>
-    <t>Order Status</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>SKU Item</t>
   </si>
   <si>
-    <t>BASECOST TRÊN SITE</t>
-  </si>
-  <si>
-    <t>Lãi &gt;10$</t>
-  </si>
-  <si>
-    <t>Est, amount</t>
-  </si>
-  <si>
     <t>30/03/2026</t>
-  </si>
-  <si>
-    <t>Tawonee Watukins Shop</t>
   </si>
   <si>
     <t>Anastasia McMullen
@@ -182,19 +50,10 @@
 Postal Code 61548</t>
   </si>
   <si>
-    <t>https://p16-oec-general-useast5.ttcdn-us.com/tos-useast5-i-omjb5zjo8w-tx/5a3fbe35dd1f456da03c164abdbec764~tplv-fhlh96nyum-origin-jpeg.jpeg?dr=12178&amp;t=555f072d&amp;ps=933b5bde&amp;shp=5d781b08&amp;shcp=54477afb&amp;idc=useast5&amp;from=1568152328</t>
-  </si>
-  <si>
-    <t>ADD</t>
-  </si>
-  <si>
     <t>https://us.shein.com/SHEIN-ICON-Plus-Size-Hippie-Women-Lace-Contrast-Allover-Print-Asymmetric-Hem-Camisole-Top-Suitable-For-Festival-Summer-Vacation-Graduation-Season-And-Back-To-School-p-88677111.html?mallCode=1&amp;main_attr=27_447</t>
   </si>
   <si>
     <t>sz25043044187451434</t>
-  </si>
-  <si>
-    <t>Hannah's Fresh Threads</t>
   </si>
   <si>
     <t>sophia correa
@@ -203,16 +62,10 @@
 Postal Code 34472</t>
   </si>
   <si>
-    <t>https://p16-oec-general-useast5.ttcdn-us.com/tos-useast5-i-omjb5zjo8w-tx/6a156a43469d4e9080de6d88c2b60078~tplv-fhlh96nyum-origin-jpeg.jpeg?dr=12178&amp;t=555f072d&amp;ps=933b5bde&amp;shp=5d781b08&amp;shcp=54477afb&amp;idc=useast5&amp;from=1568152328</t>
-  </si>
-  <si>
     <t>https://us.shein.com/ROMWE-Goth-Women-s-Fashion-Floral-Lace-Underwire-Triangle-Cup-Bra-p-179559662.html?src_identifier=st%3D2%60sc%3DGoth%20Women%27s%20Fashion%20Floral%20Lace%20Underwire%20Triangle%20Cup%20Bra%60sr%3D0%60ps%3D1&amp;src_module=search&amp;src_tab_page_id=page_goods_detail1774834800462&amp;mallCode=1&amp;pageListType=4</t>
   </si>
   <si>
     <t>si25082554047550638</t>
-  </si>
-  <si>
-    <t>Riff &amp; Rage</t>
   </si>
   <si>
     <t>Diana Batir
@@ -221,16 +74,10 @@
 Postal Code 27616</t>
   </si>
   <si>
-    <t>https://p16-oec-general-useast5.ttcdn-us.com/tos-useast5-i-omjb5zjo8w-tx/096e3eab64494f0493dbe30e998566c3~tplv-fhlh96nyum-origin-jpeg.jpeg?dr=12178&amp;t=555f072d&amp;ps=933b5bde&amp;shp=5d781b08&amp;shcp=54477afb&amp;idc=useast5&amp;from=1568152328</t>
-  </si>
-  <si>
     <t>https://us.shein.com/Hauture-Women-s-Round-Black-Pearl-Metal-Decor-Mini-Dress-p-159461305.html?src_identifier=st%3D2%60sc%3D159461305%60sr%3D0%60ps%3D1&amp;src_module=search&amp;src_tab_page_id=page_select_class1774836724556&amp;mallCode=1&amp;pageListType=4</t>
   </si>
   <si>
     <t>sz25052959983583301</t>
-  </si>
-  <si>
-    <t>Buckland Equine Rescue Inc</t>
   </si>
   <si>
     <t>Chloe Argueta
@@ -239,16 +86,10 @@
 Postal Code 30548</t>
   </si>
   <si>
-    <t>https://p16-oec-general-useast8.ttcdn-us.com/tos-useast8-i-rt0ujvrtvp-tx2/4094f37713844b1eae2d835f90a03fa3~tplv-fhlh96nyum-origin-jpeg.jpeg?dr=12178&amp;t=555f072d&amp;ps=933b5bde&amp;shp=5d781b08&amp;shcp=54477afb&amp;idc=useast5&amp;from=1568152328</t>
-  </si>
-  <si>
     <t>https://us.shein.com/SHEIN-ICON-Burgundy-Halter-Tank-Top-For-Women-Boho-Style-Knitted-Fabric-Regular-Length-p-307707045.html?src_identifier=st%3D2%60sc%3D307707045%60sr%3D0%60ps%3D1&amp;src_module=search&amp;src_tab_page_id=page_risk_crawler_block1774836540751&amp;mallCode=1&amp;pageListType=4</t>
   </si>
   <si>
     <t>sz25051954474575763</t>
-  </si>
-  <si>
-    <t>CONVERTIBLE BUILDERS LLC</t>
   </si>
   <si>
     <t>Ari Ari
@@ -257,16 +98,10 @@
 Postal Code 23666</t>
   </si>
   <si>
-    <t>https://p16-oec-general-useast8.ttcdn-us.com/tos-useast8-i-rt0ujvrtvp-tx2/2c3771c2c8c040d59251fc2e6a7a23de~tplv-fhlh96nyum-origin-jpeg.jpeg?dr=12178&amp;t=555f072d&amp;ps=933b5bde&amp;shp=5d781b08&amp;shcp=54477afb&amp;idc=useast5&amp;from=1568152328</t>
-  </si>
-  <si>
     <t>https://us.shein.com/SUMWON-WOMEN-Tank-Top-For-Women-Notch-Neck-Crop-Top-Summer-Casual-Sleeveless-p-99937361.html?mallCode=1&amp;main_attr=27_334</t>
   </si>
   <si>
     <t>sz25031959820266337</t>
-  </si>
-  <si>
-    <t>Deaena Rayae Umbaarger Shop</t>
   </si>
   <si>
     <t>trainingwithtasha Leddon
@@ -275,9 +110,6 @@
 Postal Code 30234</t>
   </si>
   <si>
-    <t>https://p16-oec-general-useast5.ttcdn-us.com/tos-useast5-i-omjb5zjo8w-tx/bb4817306398496dbf35010bbae4b1d7~tplv-fhlh96nyum-origin-jpeg.jpeg?dr=12178&amp;t=555f072d&amp;ps=933b5bde&amp;shp=5d781b08&amp;shcp=54477afb&amp;idc=useast5&amp;from=1568152328</t>
-  </si>
-  <si>
     <t>https://us.shein.com/Aloruh-Women-s-Cut-Flower-Knit-Dress-Wedding-Guest-Dress-Holiday-Dress-Graduation-Season-Dress-Date-Party-Dress-Solid-Color-Midi-Dress-Elegant-Blue-Cutout-Backless-High-Slit-Dress-Bodycon-Dress-Maxi-Dress-Party-Dresses-For-Women-Graduation-Teacher-Outfits-For-Women-Teacher-Dress-p-72614842.html?src_identifier=st%3D2%60sc%3DWomen%27s%20Cut%20Flower%20Knit%20Dress%20Wedding%20Guest%20Dress%20Holiday%20Dress%20Graduation%20Season%20Dress%20Date%20Party%20Dress%20Solid%20Color%20Midi%20Dress%20Elegant%20Blue%20Cutout%20Ba%60sr%3D0%60ps%3D1&amp;src_module=search&amp;src_tab_page_id=page_search1774834811271&amp;mallCode=1&amp;pageListType=4&amp;imgRatio=1-1&amp;detailBusinessFrom=0-1_72614842%7C0-2&amp;pageListType=4</t>
   </si>
   <si>
@@ -290,16 +122,10 @@
 Postal Code 27258</t>
   </si>
   <si>
-    <t>https://p16-oec-general-useast5.ttcdn-us.com/tos-useast5-i-omjb5zjo8w-tx/6c2e0ef9b8a9451dbf574668b011a74c~tplv-fhlh96nyum-origin-jpeg.jpeg?dr=12178&amp;t=555f072d&amp;ps=933b5bde&amp;shp=5d781b08&amp;shcp=54477afb&amp;idc=useast5&amp;from=1568152328</t>
-  </si>
-  <si>
     <t>https://us.shein.com/SHEIN-BAE-Women-s-Asymmetric-Tie-Strap-Flare-Hem-Elegant-Dress-White-Dress-For-Women-Going-Out-Valentine-s-Day-Valentine-Outfits-For-Women-p-76680817.html?mallCode=1&amp;main_attr=27_78</t>
   </si>
   <si>
     <t>sz2411209182222242</t>
-  </si>
-  <si>
-    <t>Divine Core</t>
   </si>
   <si>
     <t>Emma Allred
@@ -308,16 +134,10 @@
 Postal Code 36203</t>
   </si>
   <si>
-    <t>https://p16-oec-general-useast5.ttcdn-us.com/tos-useast5-i-omjb5zjo8w-tx/1fd2347284554797af6be9f8403cd554~tplv-fhlh96nyum-origin-jpeg.jpeg?dr=12178&amp;t=555f072d&amp;ps=933b5bde&amp;shp=5d781b08&amp;shcp=54477afb&amp;idc=useast5&amp;from=1568152328</t>
-  </si>
-  <si>
     <t>https://us.shein.com/Soleia-Women-s-Casual-Vacation-New-V-Neck-Halter-Tie-Bow-Front-Hollow-Out-Black-White-Contrast-Trim-Bodycon-Ribbed-Jumpsuit-Versatile-For-Party-Date-Afternoon-Tea-Beach-p-170226222.html?mallCode=1&amp;main_attr=27_447</t>
   </si>
   <si>
     <t>sz25052388381527999</t>
-  </si>
-  <si>
-    <t>HOME AC INC</t>
   </si>
   <si>
     <t>Ernesto Desantiago
@@ -326,25 +146,10 @@
 Postal Code 79731</t>
   </si>
   <si>
-    <t>https://p16-oec-general-useast5.ttcdn-us.com/tos-useast5-i-omjb5zjo8w-tx/764702350fba496697c9c430953b89a9~tplv-fhlh96nyum-origin-jpeg.jpeg?dr=12178&amp;t=555f072d&amp;ps=933b5bde&amp;shp=5d781b08&amp;shcp=54477afb&amp;idc=useast5&amp;from=1568152328</t>
-  </si>
-  <si>
     <t>https://us.shein.com/Palasendo-Men-s-Leopard-Print-Patch-Pocket-Drawstring-Waist-Beach-Shorts-Suitable-For-Summer-Men-Swim-Wear-p-85090738.html?src_identifier=st%3D2%60sc%3Dsm25041183733967332%60sr%3D0%60ps%3D1&amp;src_module=search&amp;src_tab_page_id=page_risk_crawler_block1774836455148&amp;mallCode=1&amp;pageListType=4&amp;imgRatio=1-1&amp;detailBusinessFrom=0-1_85090738%7C0-2&amp;pageListType=4</t>
   </si>
   <si>
     <t>sm25041183733967332</t>
-  </si>
-  <si>
-    <t>15..31</t>
-  </si>
-  <si>
-    <t>Link image</t>
-  </si>
-  <si>
-    <t>image mockup</t>
-  </si>
-  <si>
-    <t>Base Cost</t>
   </si>
   <si>
     <t>color</t>
@@ -399,7 +204,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,12 +220,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -446,7 +245,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -462,12 +261,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -514,25 +307,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -543,19 +333,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -573,110 +354,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>1</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>2</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>3</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>4</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>5</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>6</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>7</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>8</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-  <rel r:id="rId2"/>
-  <rel r:id="rId3"/>
-  <rel r:id="rId4"/>
-  <rel r:id="rId5"/>
-  <rel r:id="rId6"/>
-  <rel r:id="rId7"/>
-  <rel r:id="rId8"/>
-  <rel r:id="rId9"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -996,193 +673,130 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303B7422-C7A5-42D4-80A4-39AD87A21816}">
-  <dimension ref="A1:BX10"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="8" max="8" width="42.28515625" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-    <col min="14" max="14" width="27.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="18.5703125" customWidth="1"/>
-    <col min="17" max="17" width="20.7109375" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="73.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:76" s="7" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8"/>
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:64" s="6" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J1" s="9" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
+      <c r="AM1" s="9"/>
+      <c r="AN1" s="9"/>
+      <c r="AO1" s="9"/>
+      <c r="AP1" s="9"/>
+      <c r="AQ1" s="9"/>
+      <c r="AR1" s="9"/>
+      <c r="AS1" s="9"/>
+      <c r="AT1" s="9"/>
+      <c r="AU1" s="9"/>
+      <c r="AV1" s="9"/>
+      <c r="AW1" s="9"/>
+      <c r="AX1" s="9"/>
+      <c r="AY1" s="9"/>
+      <c r="AZ1" s="9"/>
+      <c r="BA1" s="9"/>
+      <c r="BB1" s="9"/>
+      <c r="BC1" s="9"/>
+      <c r="BD1" s="9"/>
+      <c r="BE1" s="9"/>
+      <c r="BF1" s="9"/>
+      <c r="BG1" s="9"/>
+      <c r="BH1" s="9"/>
+      <c r="BI1" s="9"/>
+      <c r="BJ1" s="9"/>
+      <c r="BK1" s="9"/>
+      <c r="BL1" s="10"/>
+    </row>
+    <row r="2" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="S1" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="T1" s="1"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
-      <c r="AJ1" s="13"/>
-      <c r="AK1" s="13"/>
-      <c r="AL1" s="13"/>
-      <c r="AM1" s="13"/>
-      <c r="AN1" s="13"/>
-      <c r="AO1" s="13"/>
-      <c r="AP1" s="13"/>
-      <c r="AQ1" s="13"/>
-      <c r="AR1" s="13"/>
-      <c r="AS1" s="13"/>
-      <c r="AT1" s="13"/>
-      <c r="AU1" s="13"/>
-      <c r="AV1" s="13"/>
-      <c r="AW1" s="13"/>
-      <c r="AX1" s="13"/>
-      <c r="AY1" s="13"/>
-      <c r="AZ1" s="13"/>
-      <c r="BA1" s="13"/>
-      <c r="BB1" s="13"/>
-      <c r="BC1" s="13"/>
-      <c r="BD1" s="13"/>
-      <c r="BE1" s="13"/>
-      <c r="BF1" s="13"/>
-      <c r="BG1" s="13"/>
-      <c r="BH1" s="13"/>
-      <c r="BI1" s="13"/>
-      <c r="BJ1" s="13"/>
-      <c r="BK1" s="13"/>
-      <c r="BL1" s="13"/>
-      <c r="BM1" s="13"/>
-      <c r="BN1" s="13"/>
-      <c r="BO1" s="13"/>
-      <c r="BP1" s="13"/>
-      <c r="BQ1" s="13"/>
-      <c r="BR1" s="13"/>
-      <c r="BS1" s="13"/>
-      <c r="BT1" s="13"/>
-      <c r="BU1" s="13"/>
-      <c r="BV1" s="13"/>
-      <c r="BW1" s="13"/>
-      <c r="BX1" s="14"/>
-    </row>
-    <row r="2" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="3">
-        <v>5.7732837717577306E+17</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="4">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="3" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" s="6">
-        <v>18.52</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>25.15</v>
-      </c>
-      <c r="R2" s="6">
-        <v>48.67</v>
-      </c>
-      <c r="S2" s="6">
-        <v>20.05</v>
-      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
@@ -1228,71 +842,41 @@
       <c r="BJ2" s="3"/>
       <c r="BK2" s="3"/>
       <c r="BL2" s="3"/>
-      <c r="BM2" s="3"/>
-      <c r="BN2" s="3"/>
-      <c r="BO2" s="3"/>
-      <c r="BP2" s="3"/>
-      <c r="BQ2" s="3"/>
-      <c r="BR2" s="3"/>
-      <c r="BS2" s="3"/>
-      <c r="BT2" s="3"/>
-      <c r="BU2" s="3"/>
-      <c r="BV2" s="3"/>
-      <c r="BW2" s="3"/>
-      <c r="BX2" s="3"/>
     </row>
-    <row r="3" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="3">
-        <v>5.7732835415631898E+17</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>65</v>
+        <v>5</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="3" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
-      <c r="M3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" s="6">
-        <v>4.47</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>23.51</v>
-      </c>
-      <c r="R3" s="6">
-        <v>32.979999999999997</v>
-      </c>
-      <c r="S3" s="6">
-        <v>9.09</v>
-      </c>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
@@ -1338,71 +922,41 @@
       <c r="BJ3" s="3"/>
       <c r="BK3" s="3"/>
       <c r="BL3" s="3"/>
-      <c r="BM3" s="3"/>
-      <c r="BN3" s="3"/>
-      <c r="BO3" s="3"/>
-      <c r="BP3" s="3"/>
-      <c r="BQ3" s="3"/>
-      <c r="BR3" s="3"/>
-      <c r="BS3" s="3"/>
-      <c r="BT3" s="3"/>
-      <c r="BU3" s="3"/>
-      <c r="BV3" s="3"/>
-      <c r="BW3" s="3"/>
-      <c r="BX3" s="3"/>
     </row>
-    <row r="4" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="3">
-        <v>5.7732835046795302E+17</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="3" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-      <c r="M4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" s="6">
-        <v>13.29</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>20.420000000000002</v>
-      </c>
-      <c r="R4" s="6">
-        <v>38.71</v>
-      </c>
-      <c r="S4" s="6">
-        <v>15.68</v>
-      </c>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -1448,71 +1002,41 @@
       <c r="BJ4" s="3"/>
       <c r="BK4" s="3"/>
       <c r="BL4" s="3"/>
-      <c r="BM4" s="3"/>
-      <c r="BN4" s="3"/>
-      <c r="BO4" s="3"/>
-      <c r="BP4" s="3"/>
-      <c r="BQ4" s="3"/>
-      <c r="BR4" s="3"/>
-      <c r="BS4" s="3"/>
-      <c r="BT4" s="3"/>
-      <c r="BU4" s="3"/>
-      <c r="BV4" s="3"/>
-      <c r="BW4" s="3"/>
-      <c r="BX4" s="3"/>
     </row>
-    <row r="5" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="3">
-        <v>5.7732834938025203E+17</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>68</v>
+        <v>11</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="3" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
-      <c r="M5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P5" s="6">
-        <v>6.88</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>18.57</v>
-      </c>
-      <c r="R5" s="6">
-        <v>30.45</v>
-      </c>
-      <c r="S5" s="6">
-        <v>12.43</v>
-      </c>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
@@ -1558,71 +1082,41 @@
       <c r="BJ5" s="3"/>
       <c r="BK5" s="3"/>
       <c r="BL5" s="3"/>
-      <c r="BM5" s="3"/>
-      <c r="BN5" s="3"/>
-      <c r="BO5" s="3"/>
-      <c r="BP5" s="3"/>
-      <c r="BQ5" s="3"/>
-      <c r="BR5" s="3"/>
-      <c r="BS5" s="3"/>
-      <c r="BT5" s="3"/>
-      <c r="BU5" s="3"/>
-      <c r="BV5" s="3"/>
-      <c r="BW5" s="3"/>
-      <c r="BX5" s="3"/>
     </row>
-    <row r="6" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="3">
-        <v>5.7732834966271206E+17</v>
-      </c>
-      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>70</v>
+      <c r="F6" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="3" t="e" vm="5">
-        <v>#VALUE!</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
-      <c r="M6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="P6" s="6">
-        <v>7.91</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>16.27</v>
-      </c>
-      <c r="R6" s="6">
-        <v>29.18</v>
-      </c>
-      <c r="S6" s="6">
-        <v>12.37</v>
-      </c>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
@@ -1668,71 +1162,41 @@
       <c r="BJ6" s="3"/>
       <c r="BK6" s="3"/>
       <c r="BL6" s="3"/>
-      <c r="BM6" s="3"/>
-      <c r="BN6" s="3"/>
-      <c r="BO6" s="3"/>
-      <c r="BP6" s="3"/>
-      <c r="BQ6" s="3"/>
-      <c r="BR6" s="3"/>
-      <c r="BS6" s="3"/>
-      <c r="BT6" s="3"/>
-      <c r="BU6" s="3"/>
-      <c r="BV6" s="3"/>
-      <c r="BW6" s="3"/>
-      <c r="BX6" s="3"/>
     </row>
-    <row r="7" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="3">
-        <v>5.7732834385609101E+17</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>70</v>
+        <v>17</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="3" t="e" vm="6">
-        <v>#VALUE!</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
-      <c r="M7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P7" s="6">
-        <v>17.239999999999998</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>16.940000000000001</v>
-      </c>
-      <c r="R7" s="6">
-        <v>39.18</v>
-      </c>
-      <c r="S7" s="6">
-        <v>16.350000000000001</v>
-      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
@@ -1778,71 +1242,41 @@
       <c r="BJ7" s="3"/>
       <c r="BK7" s="3"/>
       <c r="BL7" s="3"/>
-      <c r="BM7" s="3"/>
-      <c r="BN7" s="3"/>
-      <c r="BO7" s="3"/>
-      <c r="BP7" s="3"/>
-      <c r="BQ7" s="3"/>
-      <c r="BR7" s="3"/>
-      <c r="BS7" s="3"/>
-      <c r="BT7" s="3"/>
-      <c r="BU7" s="3"/>
-      <c r="BV7" s="3"/>
-      <c r="BW7" s="3"/>
-      <c r="BX7" s="3"/>
     </row>
-    <row r="8" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="3">
-        <v>5.7732834335755802E+17</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>71</v>
+        <v>20</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="3" t="e" vm="7">
-        <v>#VALUE!</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P8" s="6">
-        <v>12.05</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>14.3</v>
-      </c>
-      <c r="R8" s="6">
-        <v>31.35</v>
-      </c>
-      <c r="S8" s="6">
-        <v>14.56</v>
-      </c>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
@@ -1888,71 +1322,41 @@
       <c r="BJ8" s="3"/>
       <c r="BK8" s="3"/>
       <c r="BL8" s="3"/>
-      <c r="BM8" s="3"/>
-      <c r="BN8" s="3"/>
-      <c r="BO8" s="3"/>
-      <c r="BP8" s="3"/>
-      <c r="BQ8" s="3"/>
-      <c r="BR8" s="3"/>
-      <c r="BS8" s="3"/>
-      <c r="BT8" s="3"/>
-      <c r="BU8" s="3"/>
-      <c r="BV8" s="3"/>
-      <c r="BW8" s="3"/>
-      <c r="BX8" s="3"/>
     </row>
-    <row r="9" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="3">
-        <v>5.7732832927112E+17</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="4">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>68</v>
+        <v>23</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I9" s="3" t="e" vm="8">
-        <v>#VALUE!</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
-      <c r="M9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="P9" s="6">
-        <v>6.69</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>17.73</v>
-      </c>
-      <c r="R9" s="6">
-        <v>29.42</v>
-      </c>
-      <c r="S9" s="6">
-        <v>11.22</v>
-      </c>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
@@ -1998,71 +1402,41 @@
       <c r="BJ9" s="3"/>
       <c r="BK9" s="3"/>
       <c r="BL9" s="3"/>
-      <c r="BM9" s="3"/>
-      <c r="BN9" s="3"/>
-      <c r="BO9" s="3"/>
-      <c r="BP9" s="3"/>
-      <c r="BQ9" s="3"/>
-      <c r="BR9" s="3"/>
-      <c r="BS9" s="3"/>
-      <c r="BT9" s="3"/>
-      <c r="BU9" s="3"/>
-      <c r="BV9" s="3"/>
-      <c r="BW9" s="3"/>
-      <c r="BX9" s="3"/>
     </row>
-    <row r="10" spans="1:76" s="7" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="3">
-        <v>5.7732830874924198E+17</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="4">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>65</v>
+        <v>26</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="3" t="e" vm="9">
-        <v>#VALUE!</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
-      <c r="M10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="P10" s="6">
-        <v>10.35</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>14.16</v>
-      </c>
-      <c r="R10" s="6">
-        <v>29.51</v>
-      </c>
-      <c r="S10" s="6" t="s">
-        <v>56</v>
-      </c>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
@@ -2108,18 +1482,6 @@
       <c r="BJ10" s="3"/>
       <c r="BK10" s="3"/>
       <c r="BL10" s="3"/>
-      <c r="BM10" s="3"/>
-      <c r="BN10" s="3"/>
-      <c r="BO10" s="3"/>
-      <c r="BP10" s="3"/>
-      <c r="BQ10" s="3"/>
-      <c r="BR10" s="3"/>
-      <c r="BS10" s="3"/>
-      <c r="BT10" s="3"/>
-      <c r="BU10" s="3"/>
-      <c r="BV10" s="3"/>
-      <c r="BW10" s="3"/>
-      <c r="BX10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/shein.xlsx
+++ b/shein.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Tool-Buy-Shein\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Tool-buy-Shein\Tool-Buy-Shein\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17676B11-DD2D-440C-A828-8C21197EDD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F05BE9A-FFFE-45DD-B9FE-0E3895019C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3495" windowWidth="21600" windowHeight="11295" xr2:uid="{91B14417-4F65-4B5F-82C0-EBB1C5344353}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91B14417-4F65-4B5F-82C0-EBB1C5344353}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -38,9 +39,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
-    <t>SKU Item</t>
-  </si>
-  <si>
     <t>30/03/2026</t>
   </si>
   <si>
@@ -198,13 +196,16 @@
   </si>
   <si>
     <t>quantity</t>
+  </si>
+  <si>
+    <t>sku_code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -674,36 +675,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303B7422-C7A5-42D4-80A4-39AD87A21816}">
   <dimension ref="A1:BL10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="73.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="27.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="2" width="73.75" customWidth="1"/>
+    <col min="3" max="3" width="19.25" customWidth="1"/>
+    <col min="4" max="4" width="23.875" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="6" width="27.25" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="6" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:64" s="6" customFormat="1" ht="16.5" thickBot="1">
       <c r="A1" s="7"/>
       <c r="B1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>0</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="9"/>
@@ -763,27 +764,27 @@
       <c r="BK1" s="9"/>
       <c r="BL1" s="10"/>
     </row>
-    <row r="2" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
       </c>
       <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -843,27 +844,27 @@
       <c r="BK2" s="3"/>
       <c r="BL2" s="3"/>
     </row>
-    <row r="3" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -923,27 +924,27 @@
       <c r="BK3" s="3"/>
       <c r="BL3" s="3"/>
     </row>
-    <row r="4" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -1003,27 +1004,27 @@
       <c r="BK4" s="3"/>
       <c r="BL4" s="3"/>
     </row>
-    <row r="5" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -1083,27 +1084,27 @@
       <c r="BK5" s="3"/>
       <c r="BL5" s="3"/>
     </row>
-    <row r="6" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -1163,27 +1164,27 @@
       <c r="BK6" s="3"/>
       <c r="BL6" s="3"/>
     </row>
-    <row r="7" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -1243,27 +1244,27 @@
       <c r="BK7" s="3"/>
       <c r="BL7" s="3"/>
     </row>
-    <row r="8" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="F8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -1323,27 +1324,27 @@
       <c r="BK8" s="3"/>
       <c r="BL8" s="3"/>
     </row>
-    <row r="9" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -1403,27 +1404,27 @@
       <c r="BK9" s="3"/>
       <c r="BL9" s="3"/>
     </row>
-    <row r="10" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:64" s="6" customFormat="1" ht="70.5" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
